--- a/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -709,10 +709,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1830300</v>
+        <v>1842800</v>
       </c>
       <c r="E8" s="3">
-        <v>1969100</v>
+        <v>1982500</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
@@ -736,10 +736,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1220800</v>
+        <v>1229100</v>
       </c>
       <c r="E9" s="3">
-        <v>1243300</v>
+        <v>1251800</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
@@ -763,10 +763,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>609500</v>
+        <v>613700</v>
       </c>
       <c r="E10" s="3">
-        <v>725800</v>
+        <v>730700</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -857,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
         <v>1100</v>
@@ -884,10 +884,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10800</v>
+        <v>10900</v>
       </c>
       <c r="E15" s="3">
-        <v>11500</v>
+        <v>11600</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>3</v>
@@ -921,10 +921,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1192900</v>
+        <v>1201000</v>
       </c>
       <c r="E17" s="3">
-        <v>1199100</v>
+        <v>1207300</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>3</v>
@@ -948,10 +948,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>637400</v>
+        <v>641800</v>
       </c>
       <c r="E18" s="3">
-        <v>770000</v>
+        <v>775200</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>-4900</v>
       </c>
       <c r="E20" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1015,10 +1015,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>632500</v>
+        <v>636900</v>
       </c>
       <c r="E21" s="3">
-        <v>768600</v>
+        <v>773800</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1069,10 +1069,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>632500</v>
+        <v>636900</v>
       </c>
       <c r="E23" s="3">
-        <v>768600</v>
+        <v>773800</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -1096,10 +1096,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>115000</v>
+        <v>115800</v>
       </c>
       <c r="E24" s="3">
-        <v>178100</v>
+        <v>179300</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1150,10 +1150,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>517500</v>
+        <v>521000</v>
       </c>
       <c r="E26" s="3">
-        <v>590500</v>
+        <v>594600</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -1177,10 +1177,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>514200</v>
+        <v>517700</v>
       </c>
       <c r="E27" s="3">
-        <v>591000</v>
+        <v>595000</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -1315,7 +1315,7 @@
         <v>4900</v>
       </c>
       <c r="E32" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -1339,10 +1339,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>514200</v>
+        <v>517700</v>
       </c>
       <c r="E33" s="3">
-        <v>591000</v>
+        <v>595000</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -1393,10 +1393,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>514200</v>
+        <v>517700</v>
       </c>
       <c r="E35" s="3">
-        <v>591000</v>
+        <v>595000</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>3</v>
@@ -1478,10 +1478,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>127700</v>
+        <v>128600</v>
       </c>
       <c r="E41" s="3">
-        <v>85200</v>
+        <v>85800</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>3</v>
@@ -1505,10 +1505,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>479800</v>
+        <v>483000</v>
       </c>
       <c r="E42" s="3">
-        <v>365400</v>
+        <v>367900</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
@@ -1532,10 +1532,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>308200</v>
+        <v>310300</v>
       </c>
       <c r="E43" s="3">
-        <v>251400</v>
+        <v>253100</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -1559,10 +1559,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>356900</v>
+        <v>359400</v>
       </c>
       <c r="E44" s="3">
-        <v>537100</v>
+        <v>540700</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1586,10 +1586,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>23400</v>
+        <v>23500</v>
       </c>
       <c r="E45" s="3">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1613,10 +1613,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1296000</v>
+        <v>1304800</v>
       </c>
       <c r="E46" s="3">
-        <v>1257100</v>
+        <v>1265600</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
@@ -1640,10 +1640,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2909200</v>
+        <v>2929000</v>
       </c>
       <c r="E47" s="3">
-        <v>2618700</v>
+        <v>2636600</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -1667,10 +1667,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1185100</v>
+        <v>1193200</v>
       </c>
       <c r="E48" s="3">
-        <v>1112000</v>
+        <v>1119600</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1694,10 +1694,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5407300</v>
+        <v>5444100</v>
       </c>
       <c r="E49" s="3">
-        <v>5128900</v>
+        <v>5163800</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -1775,10 +1775,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>35900</v>
+        <v>36200</v>
       </c>
       <c r="E52" s="3">
-        <v>135300</v>
+        <v>136300</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -1829,10 +1829,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10833500</v>
+        <v>10907300</v>
       </c>
       <c r="E54" s="3">
-        <v>10252000</v>
+        <v>10321800</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>3</v>
@@ -1882,10 +1882,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>388500</v>
+        <v>391100</v>
       </c>
       <c r="E57" s="3">
-        <v>444300</v>
+        <v>447300</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -1909,10 +1909,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1373700</v>
+        <v>1383000</v>
       </c>
       <c r="E58" s="3">
-        <v>1333300</v>
+        <v>1342400</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -1936,10 +1936,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>121900</v>
+        <v>122700</v>
       </c>
       <c r="E59" s="3">
-        <v>161300</v>
+        <v>162400</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
@@ -1963,10 +1963,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1884100</v>
+        <v>1896900</v>
       </c>
       <c r="E60" s="3">
-        <v>1938900</v>
+        <v>1952100</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>3</v>
@@ -1990,10 +1990,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3596500</v>
+        <v>3620900</v>
       </c>
       <c r="E61" s="3">
-        <v>3033800</v>
+        <v>3054400</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2017,10 +2017,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>112800</v>
+        <v>113600</v>
       </c>
       <c r="E62" s="3">
-        <v>82300</v>
+        <v>82900</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2125,10 +2125,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6423100</v>
+        <v>6466900</v>
       </c>
       <c r="E66" s="3">
-        <v>5827600</v>
+        <v>5867300</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -2273,10 +2273,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2122800</v>
+        <v>2137300</v>
       </c>
       <c r="E72" s="3">
-        <v>1926300</v>
+        <v>1939500</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
@@ -2381,10 +2381,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4410400</v>
+        <v>4440400</v>
       </c>
       <c r="E76" s="3">
-        <v>4424400</v>
+        <v>4454500</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
@@ -2467,10 +2467,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>514200</v>
+        <v>517700</v>
       </c>
       <c r="E81" s="3">
-        <v>591000</v>
+        <v>595000</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>3</v>
@@ -2669,10 +2669,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>763300</v>
+        <v>768500</v>
       </c>
       <c r="E89" s="3">
-        <v>787400</v>
+        <v>792800</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -2709,10 +2709,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-557700</v>
+        <v>-561500</v>
       </c>
       <c r="E91" s="3">
-        <v>-659600</v>
+        <v>-664100</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -2790,10 +2790,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-887400</v>
+        <v>-893400</v>
       </c>
       <c r="E94" s="3">
-        <v>-1107400</v>
+        <v>-1115000</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -2830,10 +2830,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-469800</v>
+        <v>-473000</v>
       </c>
       <c r="E96" s="3">
-        <v>-436700</v>
+        <v>-439700</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -2938,10 +2938,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>166600</v>
+        <v>167700</v>
       </c>
       <c r="E100" s="3">
-        <v>318700</v>
+        <v>320900</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -2992,7 +2992,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>42500</v>
+        <v>42800</v>
       </c>
       <c r="E102" s="3">
         <v>-1300</v>

--- a/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>JEXYY</t>
   </si>
@@ -656,40 +656,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>3</v>
       </c>
@@ -702,20 +702,23 @@
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1842800</v>
+        <v>2098900</v>
       </c>
       <c r="E8" s="3">
-        <v>1982500</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+        <v>1831400</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1970200</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -729,20 +732,23 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1229100</v>
+        <v>1323700</v>
       </c>
       <c r="E9" s="3">
-        <v>1251800</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
+        <v>1221500</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1244000</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -756,20 +762,23 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>613700</v>
+        <v>775300</v>
       </c>
       <c r="E10" s="3">
-        <v>730700</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+        <v>609900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>726200</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -783,9 +792,12 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,8 +809,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -823,9 +836,12 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -850,9 +866,12 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -860,11 +879,11 @@
         <v>600</v>
       </c>
       <c r="E14" s="3">
+        <v>500</v>
+      </c>
+      <c r="F14" s="3">
         <v>1100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -877,20 +896,23 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="E15" s="3">
-        <v>11600</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
+        <v>10800</v>
+      </c>
+      <c r="F15" s="3">
+        <v>11500</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>3</v>
@@ -904,9 +926,12 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -915,19 +940,20 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1201000</v>
+        <v>1312400</v>
       </c>
       <c r="E17" s="3">
-        <v>1207300</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
+        <v>1193600</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1199800</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -941,20 +967,23 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>641800</v>
+        <v>786500</v>
       </c>
       <c r="E18" s="3">
-        <v>775200</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
+        <v>637800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>770400</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -968,9 +997,12 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -982,19 +1014,20 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4900</v>
       </c>
-      <c r="E20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+      <c r="F20" s="3">
+        <v>-1300</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1008,20 +1041,23 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>636900</v>
+        <v>783700</v>
       </c>
       <c r="E21" s="3">
-        <v>773800</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
+        <v>632900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>769100</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1035,9 +1071,12 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1062,20 +1101,23 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>636900</v>
+        <v>783700</v>
       </c>
       <c r="E23" s="3">
-        <v>773800</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
+        <v>632900</v>
+      </c>
+      <c r="F23" s="3">
+        <v>769100</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1089,20 +1131,23 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>115800</v>
+        <v>146800</v>
       </c>
       <c r="E24" s="3">
-        <v>179300</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+        <v>115100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>178200</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1116,9 +1161,12 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1143,20 +1191,23 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>521000</v>
+        <v>636900</v>
       </c>
       <c r="E26" s="3">
-        <v>594600</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
+        <v>517800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>590900</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1170,20 +1221,23 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>517700</v>
+        <v>609700</v>
       </c>
       <c r="E27" s="3">
-        <v>595000</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
+        <v>514500</v>
+      </c>
+      <c r="F27" s="3">
+        <v>591300</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1197,9 +1251,12 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1224,9 +1281,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,9 +1311,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,9 +1341,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1305,20 +1371,23 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>4900</v>
       </c>
-      <c r="E32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+      <c r="F32" s="3">
+        <v>1300</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1332,20 +1401,23 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>517700</v>
+        <v>609700</v>
       </c>
       <c r="E33" s="3">
-        <v>595000</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
+        <v>514500</v>
+      </c>
+      <c r="F33" s="3">
+        <v>591300</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1359,9 +1431,12 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,20 +1461,23 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>517700</v>
+        <v>609700</v>
       </c>
       <c r="E35" s="3">
-        <v>595000</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
+        <v>514500</v>
+      </c>
+      <c r="F35" s="3">
+        <v>591300</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1413,26 +1491,29 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1445,9 +1526,12 @@
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1459,8 +1543,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1472,19 +1557,20 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>128600</v>
+        <v>115200</v>
       </c>
       <c r="E41" s="3">
-        <v>85800</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
+        <v>127800</v>
+      </c>
+      <c r="F41" s="3">
+        <v>85300</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1498,20 +1584,23 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>483000</v>
+        <v>506200</v>
       </c>
       <c r="E42" s="3">
-        <v>367900</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+        <v>480100</v>
+      </c>
+      <c r="F42" s="3">
+        <v>365600</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1525,20 +1614,23 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>310300</v>
+        <v>257600</v>
       </c>
       <c r="E43" s="3">
-        <v>253100</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+        <v>308400</v>
+      </c>
+      <c r="F43" s="3">
+        <v>251500</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1552,20 +1644,23 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>359400</v>
+        <v>309200</v>
       </c>
       <c r="E44" s="3">
-        <v>540700</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
+        <v>357100</v>
+      </c>
+      <c r="F44" s="3">
+        <v>537400</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -1579,20 +1674,23 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>23500</v>
+        <v>19000</v>
       </c>
       <c r="E45" s="3">
-        <v>18100</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+        <v>23400</v>
+      </c>
+      <c r="F45" s="3">
+        <v>18000</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1606,20 +1704,23 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1304800</v>
+        <v>1207100</v>
       </c>
       <c r="E46" s="3">
-        <v>1265600</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
+        <v>1296700</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1257800</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1633,20 +1734,23 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2929000</v>
+        <v>2994900</v>
       </c>
       <c r="E47" s="3">
-        <v>2636600</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+        <v>2910900</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2620200</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -1660,20 +1764,23 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1193200</v>
+        <v>1106200</v>
       </c>
       <c r="E48" s="3">
-        <v>1119600</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+        <v>1185800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1112600</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1687,20 +1794,23 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5444100</v>
+        <v>5507300</v>
       </c>
       <c r="E49" s="3">
-        <v>5163800</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
+        <v>5410500</v>
+      </c>
+      <c r="F49" s="3">
+        <v>5131800</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -1714,9 +1824,12 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1741,9 +1854,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1768,20 +1884,23 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>36200</v>
+        <v>52400</v>
       </c>
       <c r="E52" s="3">
-        <v>136300</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+        <v>35900</v>
+      </c>
+      <c r="F52" s="3">
+        <v>135400</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -1795,9 +1914,12 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1822,20 +1944,23 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10907300</v>
+        <v>10867900</v>
       </c>
       <c r="E54" s="3">
-        <v>10321800</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
+        <v>10839800</v>
+      </c>
+      <c r="F54" s="3">
+        <v>10257900</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -1849,9 +1974,12 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1863,8 +1991,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1876,19 +2005,20 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>391100</v>
+        <v>372300</v>
       </c>
       <c r="E57" s="3">
-        <v>447300</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>388700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>444500</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -1902,20 +2032,23 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1383000</v>
+        <v>854500</v>
       </c>
       <c r="E58" s="3">
-        <v>1342400</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+        <v>1374500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1334100</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -1929,20 +2062,23 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>122700</v>
+        <v>92500</v>
       </c>
       <c r="E59" s="3">
-        <v>162400</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+        <v>122000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>161400</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -1956,20 +2092,23 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1896900</v>
+        <v>1319400</v>
       </c>
       <c r="E60" s="3">
-        <v>1952100</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
+        <v>1885200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1940000</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -1983,20 +2122,23 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3620900</v>
+        <v>3792700</v>
       </c>
       <c r="E61" s="3">
-        <v>3054400</v>
+        <v>3598500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>3035500</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2010,20 +2152,23 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>113600</v>
+        <v>106600</v>
       </c>
       <c r="E62" s="3">
-        <v>82900</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+        <v>112900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>82400</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2037,9 +2182,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2064,9 +2212,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2091,9 +2242,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2118,20 +2272,23 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6466900</v>
+        <v>6172200</v>
       </c>
       <c r="E66" s="3">
-        <v>5867300</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
+        <v>6426900</v>
+      </c>
+      <c r="F66" s="3">
+        <v>5831000</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2145,9 +2302,12 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2159,8 +2319,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2185,9 +2346,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2212,9 +2376,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2239,9 +2406,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2266,20 +2436,23 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2137300</v>
+        <v>2413800</v>
       </c>
       <c r="E72" s="3">
-        <v>1939500</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
+        <v>2124000</v>
+      </c>
+      <c r="F72" s="3">
+        <v>1927500</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2293,9 +2466,12 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2320,9 +2496,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2347,9 +2526,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2374,20 +2556,23 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4440400</v>
+        <v>4695700</v>
       </c>
       <c r="E76" s="3">
-        <v>4454500</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
+        <v>4412900</v>
+      </c>
+      <c r="F76" s="3">
+        <v>4427000</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2401,9 +2586,12 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2428,26 +2616,29 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="G80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2460,20 +2651,23 @@
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>517700</v>
+        <v>609700</v>
       </c>
       <c r="E81" s="3">
-        <v>595000</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
+        <v>514500</v>
+      </c>
+      <c r="F81" s="3">
+        <v>591300</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2487,9 +2681,12 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2501,8 +2698,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2527,9 +2725,12 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2554,9 +2755,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2581,9 +2785,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,9 +2815,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2635,9 +2845,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2662,20 +2875,23 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>768500</v>
+        <v>1021300</v>
       </c>
       <c r="E89" s="3">
-        <v>792800</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
+        <v>763700</v>
+      </c>
+      <c r="F89" s="3">
+        <v>787900</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -2689,9 +2905,12 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2703,19 +2922,20 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-561500</v>
+        <v>-525600</v>
       </c>
       <c r="E91" s="3">
-        <v>-664100</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
+        <v>-558000</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-660000</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -2729,9 +2949,12 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2756,9 +2979,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2783,20 +3009,23 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-893400</v>
+        <v>-397700</v>
       </c>
       <c r="E94" s="3">
-        <v>-1115000</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+        <v>-887900</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-1108100</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -2810,9 +3039,12 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2824,19 +3056,20 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-473000</v>
+        <v>-470700</v>
       </c>
       <c r="E96" s="3">
-        <v>-439700</v>
+        <v>-470100</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-437000</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -2850,9 +3083,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2877,9 +3113,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2904,9 +3143,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2931,20 +3173,23 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>167700</v>
+        <v>-636300</v>
       </c>
       <c r="E100" s="3">
-        <v>320900</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
+        <v>166700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>318900</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -2958,9 +3203,12 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -2985,21 +3233,24 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>42800</v>
+        <v>-12600</v>
       </c>
       <c r="E102" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3012,7 +3263,10 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
@@ -712,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2098900</v>
+        <v>2141800</v>
       </c>
       <c r="E8" s="3">
-        <v>1831400</v>
+        <v>1868800</v>
       </c>
       <c r="F8" s="3">
-        <v>1970200</v>
+        <v>2010400</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -742,13 +742,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1323700</v>
+        <v>1350700</v>
       </c>
       <c r="E9" s="3">
-        <v>1221500</v>
+        <v>1246500</v>
       </c>
       <c r="F9" s="3">
-        <v>1244000</v>
+        <v>1269400</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -772,13 +772,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>775300</v>
+        <v>791100</v>
       </c>
       <c r="E10" s="3">
-        <v>609900</v>
+        <v>622300</v>
       </c>
       <c r="F10" s="3">
-        <v>726200</v>
+        <v>741100</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -876,13 +876,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
-        <v>500</v>
-      </c>
       <c r="F14" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -906,13 +906,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10700</v>
+        <v>10900</v>
       </c>
       <c r="E15" s="3">
-        <v>10800</v>
+        <v>11000</v>
       </c>
       <c r="F15" s="3">
-        <v>11500</v>
+        <v>11700</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>3</v>
@@ -947,13 +947,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1312400</v>
+        <v>1339200</v>
       </c>
       <c r="E17" s="3">
-        <v>1193600</v>
+        <v>1218000</v>
       </c>
       <c r="F17" s="3">
-        <v>1199800</v>
+        <v>1224300</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -977,13 +977,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>786500</v>
+        <v>802600</v>
       </c>
       <c r="E18" s="3">
-        <v>637800</v>
+        <v>650800</v>
       </c>
       <c r="F18" s="3">
-        <v>770400</v>
+        <v>786100</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1021,13 +1021,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2800</v>
+        <v>-2900</v>
       </c>
       <c r="E20" s="3">
-        <v>-4900</v>
+        <v>-5000</v>
       </c>
       <c r="F20" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1051,13 +1051,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>783700</v>
+        <v>799700</v>
       </c>
       <c r="E21" s="3">
-        <v>632900</v>
+        <v>645800</v>
       </c>
       <c r="F21" s="3">
-        <v>769100</v>
+        <v>784800</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1111,13 +1111,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>783700</v>
+        <v>799700</v>
       </c>
       <c r="E23" s="3">
-        <v>632900</v>
+        <v>645800</v>
       </c>
       <c r="F23" s="3">
-        <v>769100</v>
+        <v>784800</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1141,13 +1141,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>146800</v>
+        <v>149800</v>
       </c>
       <c r="E24" s="3">
-        <v>115100</v>
+        <v>117400</v>
       </c>
       <c r="F24" s="3">
-        <v>178200</v>
+        <v>181800</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1201,13 +1201,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>636900</v>
+        <v>649900</v>
       </c>
       <c r="E26" s="3">
-        <v>517800</v>
+        <v>528400</v>
       </c>
       <c r="F26" s="3">
-        <v>590900</v>
+        <v>602900</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1231,13 +1231,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>609700</v>
+        <v>622200</v>
       </c>
       <c r="E27" s="3">
-        <v>514500</v>
+        <v>525000</v>
       </c>
       <c r="F27" s="3">
-        <v>591300</v>
+        <v>603400</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1381,13 +1381,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="E32" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="F32" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1411,13 +1411,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>609700</v>
+        <v>622200</v>
       </c>
       <c r="E33" s="3">
-        <v>514500</v>
+        <v>525000</v>
       </c>
       <c r="F33" s="3">
-        <v>591300</v>
+        <v>603400</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1471,13 +1471,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>609700</v>
+        <v>622200</v>
       </c>
       <c r="E35" s="3">
-        <v>514500</v>
+        <v>525000</v>
       </c>
       <c r="F35" s="3">
-        <v>591300</v>
+        <v>603400</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1564,13 +1564,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>115200</v>
+        <v>117500</v>
       </c>
       <c r="E41" s="3">
-        <v>127800</v>
+        <v>130400</v>
       </c>
       <c r="F41" s="3">
-        <v>85300</v>
+        <v>87000</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1594,13 +1594,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>506200</v>
+        <v>516500</v>
       </c>
       <c r="E42" s="3">
-        <v>480100</v>
+        <v>489900</v>
       </c>
       <c r="F42" s="3">
-        <v>365600</v>
+        <v>373100</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
@@ -1624,13 +1624,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>257600</v>
+        <v>262800</v>
       </c>
       <c r="E43" s="3">
-        <v>308400</v>
+        <v>314700</v>
       </c>
       <c r="F43" s="3">
-        <v>251500</v>
+        <v>256600</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1654,13 +1654,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>309200</v>
+        <v>315500</v>
       </c>
       <c r="E44" s="3">
-        <v>357100</v>
+        <v>364400</v>
       </c>
       <c r="F44" s="3">
-        <v>537400</v>
+        <v>548300</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -1684,13 +1684,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19000</v>
+        <v>19300</v>
       </c>
       <c r="E45" s="3">
-        <v>23400</v>
+        <v>23800</v>
       </c>
       <c r="F45" s="3">
-        <v>18000</v>
+        <v>18400</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1714,13 +1714,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1207100</v>
+        <v>1231700</v>
       </c>
       <c r="E46" s="3">
-        <v>1296700</v>
+        <v>1323200</v>
       </c>
       <c r="F46" s="3">
-        <v>1257800</v>
+        <v>1283500</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1744,13 +1744,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2994900</v>
+        <v>3056100</v>
       </c>
       <c r="E47" s="3">
-        <v>2910900</v>
+        <v>2970300</v>
       </c>
       <c r="F47" s="3">
-        <v>2620200</v>
+        <v>2673700</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -1774,13 +1774,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1106200</v>
+        <v>1128700</v>
       </c>
       <c r="E48" s="3">
-        <v>1185800</v>
+        <v>1210000</v>
       </c>
       <c r="F48" s="3">
-        <v>1112600</v>
+        <v>1135300</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1804,13 +1804,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5507300</v>
+        <v>5619700</v>
       </c>
       <c r="E49" s="3">
-        <v>5410500</v>
+        <v>5520900</v>
       </c>
       <c r="F49" s="3">
-        <v>5131800</v>
+        <v>5236600</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -1894,13 +1894,13 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>52400</v>
+        <v>53500</v>
       </c>
       <c r="E52" s="3">
-        <v>35900</v>
+        <v>36700</v>
       </c>
       <c r="F52" s="3">
-        <v>135400</v>
+        <v>138200</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -1954,13 +1954,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10867900</v>
+        <v>11089700</v>
       </c>
       <c r="E54" s="3">
-        <v>10839800</v>
+        <v>11061100</v>
       </c>
       <c r="F54" s="3">
-        <v>10257900</v>
+        <v>10467300</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -2012,13 +2012,13 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>372300</v>
+        <v>379900</v>
       </c>
       <c r="E57" s="3">
-        <v>388700</v>
+        <v>396600</v>
       </c>
       <c r="F57" s="3">
-        <v>444500</v>
+        <v>453600</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2042,13 +2042,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>854500</v>
+        <v>872000</v>
       </c>
       <c r="E58" s="3">
-        <v>1374500</v>
+        <v>1402500</v>
       </c>
       <c r="F58" s="3">
-        <v>1334100</v>
+        <v>1361300</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -2072,13 +2072,13 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>92500</v>
+        <v>94400</v>
       </c>
       <c r="E59" s="3">
-        <v>122000</v>
+        <v>124500</v>
       </c>
       <c r="F59" s="3">
-        <v>161400</v>
+        <v>164700</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2102,13 +2102,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1319400</v>
+        <v>1346300</v>
       </c>
       <c r="E60" s="3">
-        <v>1885200</v>
+        <v>1923600</v>
       </c>
       <c r="F60" s="3">
-        <v>1940000</v>
+        <v>1979600</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -2132,13 +2132,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3792700</v>
+        <v>3870200</v>
       </c>
       <c r="E61" s="3">
-        <v>3598500</v>
+        <v>3672000</v>
       </c>
       <c r="F61" s="3">
-        <v>3035500</v>
+        <v>3097500</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>106600</v>
+        <v>108800</v>
       </c>
       <c r="E62" s="3">
-        <v>112900</v>
+        <v>115200</v>
       </c>
       <c r="F62" s="3">
-        <v>82400</v>
+        <v>84100</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2282,13 +2282,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6172200</v>
+        <v>6298200</v>
       </c>
       <c r="E66" s="3">
-        <v>6426900</v>
+        <v>6558000</v>
       </c>
       <c r="F66" s="3">
-        <v>5831000</v>
+        <v>5950000</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2446,13 +2446,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2413800</v>
+        <v>2463100</v>
       </c>
       <c r="E72" s="3">
-        <v>2124000</v>
+        <v>2167400</v>
       </c>
       <c r="F72" s="3">
-        <v>1927500</v>
+        <v>1966800</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2566,13 +2566,13 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4695700</v>
+        <v>4791500</v>
       </c>
       <c r="E76" s="3">
-        <v>4412900</v>
+        <v>4503000</v>
       </c>
       <c r="F76" s="3">
-        <v>4427000</v>
+        <v>4517300</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2661,13 +2661,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>609700</v>
+        <v>622200</v>
       </c>
       <c r="E81" s="3">
-        <v>514500</v>
+        <v>525000</v>
       </c>
       <c r="F81" s="3">
-        <v>591300</v>
+        <v>603400</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2885,13 +2885,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1021300</v>
+        <v>1042200</v>
       </c>
       <c r="E89" s="3">
-        <v>763700</v>
+        <v>779300</v>
       </c>
       <c r="F89" s="3">
-        <v>787900</v>
+        <v>804000</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -2929,13 +2929,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-525600</v>
+        <v>-536300</v>
       </c>
       <c r="E91" s="3">
-        <v>-558000</v>
+        <v>-569400</v>
       </c>
       <c r="F91" s="3">
-        <v>-660000</v>
+        <v>-673500</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -3019,13 +3019,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-397700</v>
+        <v>-405800</v>
       </c>
       <c r="E94" s="3">
-        <v>-887900</v>
+        <v>-906000</v>
       </c>
       <c r="F94" s="3">
-        <v>-1108100</v>
+        <v>-1130700</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -3063,13 +3063,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-470700</v>
+        <v>-480300</v>
       </c>
       <c r="E96" s="3">
-        <v>-470100</v>
+        <v>-479700</v>
       </c>
       <c r="F96" s="3">
-        <v>-437000</v>
+        <v>-445900</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3183,13 +3183,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-636300</v>
+        <v>-649300</v>
       </c>
       <c r="E100" s="3">
-        <v>166700</v>
+        <v>170100</v>
       </c>
       <c r="F100" s="3">
-        <v>318900</v>
+        <v>325400</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -3243,13 +3243,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-12600</v>
+        <v>-12900</v>
       </c>
       <c r="E102" s="3">
-        <v>42500</v>
+        <v>43400</v>
       </c>
       <c r="F102" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>JEXYY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -690,17 +690,17 @@
       <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="G7" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H7" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -712,25 +712,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2141800</v>
+        <v>2142500</v>
       </c>
       <c r="E8" s="3">
-        <v>1868800</v>
+        <v>1921900</v>
       </c>
       <c r="F8" s="3">
-        <v>2010400</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>2244800</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1230400</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1447400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1449500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1453200</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -742,25 +742,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1350700</v>
+        <v>1351500</v>
       </c>
       <c r="E9" s="3">
-        <v>1246500</v>
+        <v>1282600</v>
       </c>
       <c r="F9" s="3">
-        <v>1269400</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>1417900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>718100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>657400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>665700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>666600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -772,25 +772,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>791100</v>
+        <v>791000</v>
       </c>
       <c r="E10" s="3">
-        <v>622300</v>
+        <v>639300</v>
       </c>
       <c r="F10" s="3">
-        <v>741100</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>826900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>512300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>790000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>783700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>786600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -876,25 +876,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>700</v>
+        <v>-11000</v>
       </c>
       <c r="E14" s="3">
-        <v>600</v>
+        <v>18100</v>
       </c>
       <c r="F14" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-80400</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="J14" s="3">
+        <v>34800</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -906,25 +906,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10900</v>
+        <v>354200</v>
       </c>
       <c r="E15" s="3">
-        <v>11000</v>
+        <v>294900</v>
       </c>
       <c r="F15" s="3">
-        <v>11700</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>339900</v>
+      </c>
+      <c r="G15" s="3">
+        <v>248900</v>
+      </c>
+      <c r="H15" s="3">
+        <v>224100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>213100</v>
+      </c>
+      <c r="J15" s="3">
+        <v>217700</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -947,25 +947,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1339200</v>
+        <v>1401200</v>
       </c>
       <c r="E17" s="3">
-        <v>1218000</v>
+        <v>1351800</v>
       </c>
       <c r="F17" s="3">
-        <v>1224300</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>1503600</v>
+      </c>
+      <c r="G17" s="3">
+        <v>771200</v>
+      </c>
+      <c r="H17" s="3">
+        <v>713300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>725700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>710300</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -977,25 +977,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>802600</v>
+        <v>741300</v>
       </c>
       <c r="E18" s="3">
-        <v>650800</v>
+        <v>570100</v>
       </c>
       <c r="F18" s="3">
-        <v>786100</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>741200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>459200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>734100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>723800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>742900</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1021,25 +1021,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2900</v>
+        <v>10900</v>
       </c>
       <c r="E20" s="3">
-        <v>-5000</v>
+        <v>1900</v>
       </c>
       <c r="F20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>1300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H20" s="3">
+        <v>600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1051,25 +1051,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>799700</v>
+        <v>1084600</v>
       </c>
       <c r="E21" s="3">
-        <v>645800</v>
+        <v>863100</v>
       </c>
       <c r="F21" s="3">
-        <v>784800</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>1079800</v>
+      </c>
+      <c r="G21" s="3">
+        <v>708700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>957600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>933300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>960500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1081,25 +1081,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>151800</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>159300</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>137000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>66800</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>66400</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>72600</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>72500</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>799700</v>
+        <v>799900</v>
       </c>
       <c r="E23" s="3">
-        <v>645800</v>
+        <v>664200</v>
       </c>
       <c r="F23" s="3">
-        <v>784800</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>876200</v>
+      </c>
+      <c r="G23" s="3">
+        <v>495300</v>
+      </c>
+      <c r="H23" s="3">
+        <v>793000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>821900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>724500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>149800</v>
+        <v>149900</v>
       </c>
       <c r="E24" s="3">
-        <v>117400</v>
+        <v>120800</v>
       </c>
       <c r="F24" s="3">
-        <v>181800</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>203000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>109500</v>
+      </c>
+      <c r="H24" s="3">
+        <v>175400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>171100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>158100</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1201,25 +1201,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>649900</v>
+        <v>650100</v>
       </c>
       <c r="E26" s="3">
-        <v>528400</v>
+        <v>543400</v>
       </c>
       <c r="F26" s="3">
-        <v>602900</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>673200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>385800</v>
+      </c>
+      <c r="H26" s="3">
+        <v>617600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>650800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>566300</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1231,25 +1231,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>622200</v>
+        <v>622400</v>
       </c>
       <c r="E27" s="3">
-        <v>525000</v>
+        <v>540000</v>
       </c>
       <c r="F27" s="3">
-        <v>603400</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>673700</v>
+      </c>
+      <c r="G27" s="3">
+        <v>377400</v>
+      </c>
+      <c r="H27" s="3">
+        <v>603100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>636400</v>
+      </c>
+      <c r="J27" s="3">
+        <v>551400</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1381,25 +1381,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2900</v>
+        <v>-10900</v>
       </c>
       <c r="E32" s="3">
-        <v>5000</v>
+        <v>-1900</v>
       </c>
       <c r="F32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-1300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>600</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1411,25 +1411,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>622200</v>
+        <v>622400</v>
       </c>
       <c r="E33" s="3">
-        <v>525000</v>
+        <v>539900</v>
       </c>
       <c r="F33" s="3">
-        <v>603400</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>673700</v>
+      </c>
+      <c r="G33" s="3">
+        <v>377400</v>
+      </c>
+      <c r="H33" s="3">
+        <v>603200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>636300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>551400</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1471,25 +1471,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>622200</v>
+        <v>622400</v>
       </c>
       <c r="E35" s="3">
-        <v>525000</v>
+        <v>539900</v>
       </c>
       <c r="F35" s="3">
-        <v>603400</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>673700</v>
+      </c>
+      <c r="G35" s="3">
+        <v>377400</v>
+      </c>
+      <c r="H35" s="3">
+        <v>603200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>636300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>551400</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1514,17 +1514,17 @@
       <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="G38" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H38" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1564,25 +1564,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>117500</v>
+        <v>121600</v>
       </c>
       <c r="E41" s="3">
-        <v>130400</v>
+        <v>135300</v>
       </c>
       <c r="F41" s="3">
-        <v>87000</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>98200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>59200</v>
+      </c>
+      <c r="H41" s="3">
+        <v>72300</v>
+      </c>
+      <c r="I41" s="3">
+        <v>94500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>41400</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1594,25 +1594,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>516500</v>
+        <v>516700</v>
       </c>
       <c r="E42" s="3">
-        <v>489900</v>
+        <v>503800</v>
       </c>
       <c r="F42" s="3">
-        <v>373100</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>416600</v>
+      </c>
+      <c r="G42" s="3">
+        <v>234900</v>
+      </c>
+      <c r="H42" s="3">
+        <v>97200</v>
+      </c>
+      <c r="I42" s="3">
+        <v>99400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>81500</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1624,25 +1624,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>262800</v>
+        <v>259500</v>
       </c>
       <c r="E43" s="3">
-        <v>314700</v>
+        <v>322900</v>
       </c>
       <c r="F43" s="3">
-        <v>256600</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>253300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>113800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>39600</v>
+      </c>
+      <c r="I43" s="3">
+        <v>52400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>110000</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1654,25 +1654,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>315500</v>
+        <v>315700</v>
       </c>
       <c r="E44" s="3">
-        <v>364400</v>
+        <v>374800</v>
       </c>
       <c r="F44" s="3">
-        <v>548300</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>612300</v>
+      </c>
+      <c r="G44" s="3">
+        <v>635400</v>
+      </c>
+      <c r="H44" s="3">
+        <v>598100</v>
+      </c>
+      <c r="I44" s="3">
+        <v>588200</v>
+      </c>
+      <c r="J44" s="3">
+        <v>462700</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1684,25 +1684,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19300</v>
+        <v>13100</v>
       </c>
       <c r="E45" s="3">
-        <v>23800</v>
+        <v>16500</v>
       </c>
       <c r="F45" s="3">
-        <v>18400</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>44500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>97300</v>
+      </c>
+      <c r="H45" s="3">
+        <v>40100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2200</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1714,25 +1714,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1231700</v>
+        <v>1232100</v>
       </c>
       <c r="E46" s="3">
-        <v>1323200</v>
+        <v>1360800</v>
       </c>
       <c r="F46" s="3">
-        <v>1283500</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>1433100</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1154500</v>
+      </c>
+      <c r="H46" s="3">
+        <v>865500</v>
+      </c>
+      <c r="I46" s="3">
+        <v>857700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>707300</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1744,25 +1744,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3056100</v>
+        <v>3048700</v>
       </c>
       <c r="E47" s="3">
-        <v>2970300</v>
+        <v>3038400</v>
       </c>
       <c r="F47" s="3">
-        <v>2673700</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>2985400</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2242600</v>
+      </c>
+      <c r="H47" s="3">
+        <v>2016500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1432000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1145500</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1774,25 +1774,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1128700</v>
+        <v>1087000</v>
       </c>
       <c r="E48" s="3">
-        <v>1210000</v>
+        <v>1198200</v>
       </c>
       <c r="F48" s="3">
-        <v>1135300</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>1251500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2657200</v>
+      </c>
+      <c r="H48" s="3">
+        <v>2356700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1730500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1542200</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1804,25 +1804,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5619700</v>
+        <v>5621500</v>
       </c>
       <c r="E49" s="3">
-        <v>5520900</v>
+        <v>5677800</v>
       </c>
       <c r="F49" s="3">
-        <v>5236600</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>5847100</v>
+      </c>
+      <c r="G49" s="3">
+        <v>3262400</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2718400</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2948700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3068000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1894,25 +1894,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>53500</v>
+        <v>75400</v>
       </c>
       <c r="E52" s="3">
-        <v>36700</v>
+        <v>70900</v>
       </c>
       <c r="F52" s="3">
-        <v>138200</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>142800</v>
+      </c>
+      <c r="G52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>4800</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -1954,25 +1954,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11089700</v>
+        <v>11093300</v>
       </c>
       <c r="E54" s="3">
-        <v>11061100</v>
+        <v>11375400</v>
       </c>
       <c r="F54" s="3">
-        <v>10467300</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>11687600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>9358100</v>
+      </c>
+      <c r="H54" s="3">
+        <v>7988800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>7002700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>6536700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2012,25 +2012,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>379900</v>
+        <v>415700</v>
       </c>
       <c r="E57" s="3">
-        <v>396600</v>
+        <v>461000</v>
       </c>
       <c r="F57" s="3">
-        <v>453600</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>527600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>266500</v>
+      </c>
+      <c r="H57" s="3">
+        <v>181300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>144000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>128300</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2042,25 +2042,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>872000</v>
+        <v>836600</v>
       </c>
       <c r="E58" s="3">
-        <v>1402500</v>
+        <v>1389300</v>
       </c>
       <c r="F58" s="3">
-        <v>1361300</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>1498900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1659700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1455200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>620400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>993800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2072,25 +2072,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>94400</v>
+        <v>64500</v>
       </c>
       <c r="E59" s="3">
-        <v>124500</v>
+        <v>73100</v>
       </c>
       <c r="F59" s="3">
-        <v>164700</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>135300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>200500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>233100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>212100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>183900</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2102,25 +2102,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1346300</v>
+        <v>1346700</v>
       </c>
       <c r="E60" s="3">
-        <v>1923600</v>
+        <v>1978300</v>
       </c>
       <c r="F60" s="3">
-        <v>1979600</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>2210400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2149500</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1884500</v>
+      </c>
+      <c r="I60" s="3">
+        <v>995300</v>
+      </c>
+      <c r="J60" s="3">
+        <v>1340700</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2132,25 +2132,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3870200</v>
+        <v>3871400</v>
       </c>
       <c r="E61" s="3">
-        <v>3672000</v>
+        <v>3776300</v>
       </c>
       <c r="F61" s="3">
-        <v>3097500</v>
+        <v>3459300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2074200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1340400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1696700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1205600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2162,25 +2162,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>108800</v>
+        <v>9800</v>
       </c>
       <c r="E62" s="3">
-        <v>115200</v>
+        <v>10400</v>
       </c>
       <c r="F62" s="3">
-        <v>84100</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>11500</v>
+      </c>
+      <c r="G62" s="3">
+        <v>8300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1200</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2282,25 +2282,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6298200</v>
+        <v>5327000</v>
       </c>
       <c r="E66" s="3">
-        <v>6558000</v>
+        <v>5873100</v>
       </c>
       <c r="F66" s="3">
-        <v>5950000</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>5762900</v>
+      </c>
+      <c r="G66" s="3">
+        <v>4295900</v>
+      </c>
+      <c r="H66" s="3">
+        <v>3294900</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2734800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>2557000</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2446,25 +2446,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2463100</v>
+        <v>2463600</v>
       </c>
       <c r="E72" s="3">
-        <v>2167400</v>
+        <v>2228900</v>
       </c>
       <c r="F72" s="3">
-        <v>1966800</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>2196100</v>
+      </c>
+      <c r="G72" s="3">
+        <v>1817000</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1682600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>1429700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1179300</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2566,25 +2566,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4791500</v>
+        <v>4793100</v>
       </c>
       <c r="E76" s="3">
-        <v>4503000</v>
+        <v>4631000</v>
       </c>
       <c r="F76" s="3">
-        <v>4517300</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>5044000</v>
+      </c>
+      <c r="G76" s="3">
+        <v>4321000</v>
+      </c>
+      <c r="H76" s="3">
+        <v>4099900</v>
+      </c>
+      <c r="I76" s="3">
+        <v>3800300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>3614800</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2639,17 +2639,17 @@
       <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="G80" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H80" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2661,25 +2661,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>622200</v>
+        <v>622400</v>
       </c>
       <c r="E81" s="3">
-        <v>525000</v>
+        <v>539900</v>
       </c>
       <c r="F81" s="3">
-        <v>603400</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>673700</v>
+      </c>
+      <c r="G81" s="3">
+        <v>377400</v>
+      </c>
+      <c r="H81" s="3">
+        <v>603200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>636300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>551400</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2705,25 +2705,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>95700</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>77800</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>30700</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>29500</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>33800</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -2885,25 +2885,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1042200</v>
+        <v>1042500</v>
       </c>
       <c r="E89" s="3">
-        <v>779300</v>
+        <v>801500</v>
       </c>
       <c r="F89" s="3">
-        <v>804000</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>897700</v>
+      </c>
+      <c r="G89" s="3">
+        <v>480600</v>
+      </c>
+      <c r="H89" s="3">
+        <v>827700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>831000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>804100</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -2929,25 +2929,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-536300</v>
+        <v>-536500</v>
       </c>
       <c r="E91" s="3">
-        <v>-569400</v>
+        <v>-585600</v>
       </c>
       <c r="F91" s="3">
-        <v>-673500</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-752000</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-650300</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-696500</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-515500</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1137000</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3019,25 +3019,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-405800</v>
+        <v>-406000</v>
       </c>
       <c r="E94" s="3">
-        <v>-906000</v>
+        <v>-931800</v>
       </c>
       <c r="F94" s="3">
-        <v>-1130700</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-1262500</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-873100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-1061600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-694100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1165400</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3063,25 +3063,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-480300</v>
+        <v>480400</v>
       </c>
       <c r="E96" s="3">
-        <v>-479700</v>
+        <v>493300</v>
       </c>
       <c r="F96" s="3">
-        <v>-445900</v>
+        <v>497900</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>467600</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>391300</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>400700</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3183,25 +3183,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-649300</v>
+        <v>-649500</v>
       </c>
       <c r="E100" s="3">
-        <v>170100</v>
+        <v>174900</v>
       </c>
       <c r="F100" s="3">
-        <v>325400</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>363300</v>
+      </c>
+      <c r="G100" s="3">
+        <v>377400</v>
+      </c>
+      <c r="H100" s="3">
+        <v>224400</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-100300</v>
+      </c>
+      <c r="J100" s="3">
+        <v>371800</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3212,26 +3212,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3246,22 +3246,22 @@
         <v>-12900</v>
       </c>
       <c r="E102" s="3">
-        <v>43400</v>
+        <v>44600</v>
       </c>
       <c r="F102" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>36700</v>
+      </c>
+      <c r="J102" s="3">
+        <v>10500</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>JEXYY</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3178200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2142500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1921900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2244800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1230400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1447400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1449500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1453200</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2343400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1351500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1282600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1417900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>718100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>657400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>665700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>666600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>834800</v>
+      </c>
+      <c r="E10" s="3">
         <v>791000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>639300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>826900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>512300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>790000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>783700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>786600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +822,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-11000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-80400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-9500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-21900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>34800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>354200</v>
+        <v>346300</v>
       </c>
       <c r="E15" s="3">
+        <v>354800</v>
+      </c>
+      <c r="F15" s="3">
         <v>294900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>339900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>248900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>224100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>213100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>217700</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2402700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1401200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1351800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1503600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>771200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>713300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>725700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>710300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>775500</v>
+      </c>
+      <c r="E18" s="3">
         <v>741300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>570100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>741200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>459200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>734100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>723800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>742900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,158 +1047,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>10900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1084600</v>
+        <v>1122600</v>
       </c>
       <c r="E21" s="3">
+        <v>1085200</v>
+      </c>
+      <c r="F21" s="3">
         <v>863100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1079800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>708700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>957600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>933300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>960500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E22" s="3">
         <v>151800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>159300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>137000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>66800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>72600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>72500</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>865400</v>
+      </c>
+      <c r="E23" s="3">
         <v>799900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>664200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>876200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>495300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>793000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>821900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>724500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E24" s="3">
         <v>149900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>120800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>203000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>109500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>175400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>171100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>158100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>708400</v>
+      </c>
+      <c r="E26" s="3">
         <v>650100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>543400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>673200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>385800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>617600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>650800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>566300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>677700</v>
+      </c>
+      <c r="E27" s="3">
         <v>622400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>540000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>673700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>377400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>603100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>636400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>551400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>677700</v>
+      </c>
+      <c r="E33" s="3">
         <v>622400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>539900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>673700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>377400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>603200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>636300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>551400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>677700</v>
+      </c>
+      <c r="E35" s="3">
         <v>622400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>539900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>673700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>377400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>603200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>636300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>551400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,278 +1643,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>118400</v>
+      </c>
+      <c r="E41" s="3">
         <v>121600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>135300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>98200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>72300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41400</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>427700</v>
+      </c>
+      <c r="E42" s="3">
         <v>516700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>503800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>416600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>234900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>97200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>99400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>81500</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>316500</v>
+      </c>
+      <c r="E43" s="3">
         <v>259500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>322900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>253300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>39600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>52400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>110000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>273900</v>
+      </c>
+      <c r="E44" s="3">
         <v>315700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>374800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>612300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>635400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>598100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>588200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>462700</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E45" s="3">
         <v>13100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>44500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>97300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>40100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1150000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1232100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1360800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1433100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1154500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>865500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>857700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>707300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3403800</v>
+      </c>
+      <c r="E47" s="3">
         <v>3048700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3038400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2985400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2242600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2016500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1432000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1145500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1017600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1087000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1198200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1251500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2657200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2356700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1730500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1542200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6574500</v>
+      </c>
+      <c r="E49" s="3">
         <v>5621500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5677800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5847100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3262400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2718400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2948700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3068000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,39 +2003,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>75400</v>
+        <v>141200</v>
       </c>
       <c r="E52" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F52" s="3">
         <v>70900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>142800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12314700</v>
+      </c>
+      <c r="E54" s="3">
         <v>11093300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11375400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11687600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9358100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7988800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7002700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6536700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,188 +2135,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>317800</v>
+      </c>
+      <c r="E57" s="3">
         <v>415700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>461000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>527600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>266500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>181300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>144000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>128300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1811000</v>
+      </c>
+      <c r="E58" s="3">
         <v>836600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1389300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1498900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1659700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1455200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>620400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>993800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E59" s="3">
         <v>64500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>73100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>135300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>200500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>233100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>212100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>183900</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2217600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1346700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1978300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2210400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2149500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1884500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>995300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1340700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3095500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3871400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3776300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3459300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2074200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1340400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1696700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1205600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E62" s="3">
         <v>9800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5501000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5327000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5873100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5762900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4295900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3294900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2734800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2557000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2746600</v>
+      </c>
+      <c r="E72" s="3">
         <v>2463600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2228900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2196100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1817000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1682600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1429700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1179300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5287900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4793100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4631000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5044000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4321000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4099900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3800300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3614800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>677700</v>
+      </c>
+      <c r="E81" s="3">
         <v>622400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>539900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>673700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>377400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>603200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>636300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>551400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E83" s="3">
         <v>95700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>88700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>77800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>30700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>33800</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>865300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1042500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>801500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>897700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>480600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>827700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>831000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>804100</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1479900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-536500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-585600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-752000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-650300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-696500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-515500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1286100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-406000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-931800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1262500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-873100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1061600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-694100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1165400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,38 +3289,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>456300</v>
+      </c>
+      <c r="E96" s="3">
         <v>480400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>493300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>497900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>467600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>391300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>418000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>400700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,39 +3418,45 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>422100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-649500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>174900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>363300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>377400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>224400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>371800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3233,40 +3481,46 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>44600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>36700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10500</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JEXYY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>JEXYY</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2900800</v>
+      </c>
+      <c r="E8" s="3">
         <v>3178200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2142500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1921900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2244800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1230400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1447400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1449500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1453200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2343400</v>
+        <v>2028500</v>
       </c>
       <c r="E9" s="3">
+        <v>2342900</v>
+      </c>
+      <c r="F9" s="3">
         <v>1351500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1282600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1417900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>718100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>657400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>665700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>666600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>834800</v>
+        <v>872300</v>
       </c>
       <c r="E10" s="3">
+        <v>835300</v>
+      </c>
+      <c r="F10" s="3">
         <v>791000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>639300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>826900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>512300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>790000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>783700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>786600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,13 +835,14 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,75 +904,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E14" s="3">
         <v>24900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-11000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>18100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-80400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-9500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-21900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>34800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>346300</v>
+        <v>369800</v>
       </c>
       <c r="E15" s="3">
+        <v>346800</v>
+      </c>
+      <c r="F15" s="3">
         <v>354800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>294900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>339900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>248900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>224100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>213100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>217700</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2085000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2402700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1401200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1351800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1503600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>771200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>713300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>725700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>710300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>815800</v>
+      </c>
+      <c r="E18" s="3">
         <v>775500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>741300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>570100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>741200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>459200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>734100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>723800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>742900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,173 +1080,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-900</v>
+        <v>1000</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>10900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1122600</v>
+        <v>1184600</v>
       </c>
       <c r="E21" s="3">
+        <v>1122500</v>
+      </c>
+      <c r="F21" s="3">
         <v>1085200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>863100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1079800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>708700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>957600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>933300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>960500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E22" s="3">
         <v>132000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>151800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>159300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>137000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>66400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>72600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>72500</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>872900</v>
+      </c>
+      <c r="E23" s="3">
         <v>865400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>799900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>664200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>876200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>495300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>793000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>821900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>724500</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>183600</v>
+      </c>
+      <c r="E24" s="3">
         <v>157100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>149900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>120800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>203000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>109500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>175400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>171100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>158100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>689300</v>
+      </c>
+      <c r="E26" s="3">
         <v>708400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>650100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>543400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>673200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>385800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>617600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>650800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>566300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>656800</v>
+      </c>
+      <c r="E27" s="3">
         <v>677700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>622400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>540000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>673700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>377400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>603100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>636400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>551400</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>900</v>
+        <v>-1000</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-10900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>656800</v>
+      </c>
+      <c r="E33" s="3">
         <v>677700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>622400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>539900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>673700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>377400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>603200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>636300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>551400</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>656800</v>
+      </c>
+      <c r="E35" s="3">
         <v>677700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>622400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>539900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>673700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>377400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>603200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>636300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>551400</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,305 +1729,333 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>87400</v>
+      </c>
+      <c r="E41" s="3">
         <v>118400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>121600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>135300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>98200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>59200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>94500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>263200</v>
+      </c>
+      <c r="E42" s="3">
         <v>427700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>516700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>503800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>416600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>234900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>97200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>99400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>81500</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>321400</v>
+      </c>
+      <c r="E43" s="3">
         <v>316500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>259500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>322900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>253300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>113800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>52400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>110000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>268200</v>
+      </c>
+      <c r="E44" s="3">
         <v>273900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>315700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>374800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>612300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>635400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>598100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>588200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>462700</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E45" s="3">
         <v>12900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>44500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>97300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>40100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>964600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1150000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1232100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1360800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1433100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1154500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>865500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>857700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>707300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3759000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3403800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3048700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3038400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2985400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2242600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2016500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1432000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1145500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1196200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1017600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1087000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1198200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1251500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2657200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2356700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1730500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1542200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7665900</v>
+      </c>
+      <c r="E49" s="3">
         <v>6574500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5621500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5677800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5847100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3262400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2718400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2948700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3068000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E52" s="3">
         <v>141200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>70900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>142800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13780900</v>
+      </c>
+      <c r="E54" s="3">
         <v>12314700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11093300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11375400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11687600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9358100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7988800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7002700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6536700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,206 +2265,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>538100</v>
+      </c>
+      <c r="E57" s="3">
         <v>317800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>415700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>461000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>527600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>266500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>181300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>144000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>128300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1008400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1811000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>836600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1389300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1498900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1659700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1455200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>620400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>993800</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E59" s="3">
         <v>55000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>64500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>135300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>200500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>233100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>212100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>183900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1640800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2217600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1346700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1978300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2210400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2149500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1884500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>995300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1340700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4043900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3095500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3871400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3776300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3459300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2074200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1340400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1696700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1205600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E62" s="3">
         <v>9300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5920200</v>
+      </c>
+      <c r="E66" s="3">
         <v>5501000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5327000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5873100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5762900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4295900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3294900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2734800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2557000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3170200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2746600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2463600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2228900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2196100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1817000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1682600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1429700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1179300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5925100</v>
+      </c>
+      <c r="E76" s="3">
         <v>5287900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4793100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4631000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5044000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4321000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4099900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3800300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3614800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>656800</v>
+      </c>
+      <c r="E81" s="3">
         <v>677700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>622400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>539900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>673700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>377400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>603200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>636300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>551400</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>110900</v>
+      </c>
+      <c r="E83" s="3">
         <v>97800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>95700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>88700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>77800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>33600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>30700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33800</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>966700</v>
+      </c>
+      <c r="E89" s="3">
         <v>865300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1042500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>801500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>897700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>480600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>827700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>831000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>804100</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1090300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1479900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-536500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-585600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-752000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-650300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-696500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-515500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-760900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1286100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-406000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-931800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1262500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-873100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1061600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-694100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1165400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,41 +3522,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>474700</v>
+      </c>
+      <c r="E96" s="3">
         <v>456300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>480400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>493300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>497900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>467600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>391300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>418000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>400700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,42 +3663,48 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-239900</v>
+      </c>
+      <c r="E100" s="3">
         <v>422100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-649500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>174900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>363300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>377400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>224400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>371800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3484,43 +3732,49 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>44600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>36700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
